--- a/Report_ScuolaDb.xlsx
+++ b/Report_ScuolaDb.xlsx
@@ -7,42 +7,20 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="sysdiagrams" sheetId="1" r:id="rId1"/>
-    <sheet name="Studenti" sheetId="2" r:id="rId2"/>
-    <sheet name="Corsi" sheetId="3" r:id="rId3"/>
-    <sheet name="Docenti" sheetId="4" r:id="rId4"/>
-    <sheet name="Aule" sheetId="5" r:id="rId5"/>
-    <sheet name="Iscrizioni" sheetId="6" r:id="rId6"/>
-    <sheet name="Lezioni" sheetId="7" r:id="rId7"/>
-    <sheet name="DocentiCorso" sheetId="8" r:id="rId8"/>
+    <sheet name="Studenti" sheetId="1" r:id="rId1"/>
+    <sheet name="Corsi" sheetId="2" r:id="rId2"/>
+    <sheet name="Docenti" sheetId="3" r:id="rId3"/>
+    <sheet name="Aule" sheetId="4" r:id="rId4"/>
+    <sheet name="Iscrizioni" sheetId="5" r:id="rId5"/>
+    <sheet name="Lezioni" sheetId="6" r:id="rId6"/>
+    <sheet name="DocentiCorso" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="360">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>principal_id</t>
-  </si>
-  <si>
-    <t>diagram_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>definition</t>
-  </si>
-  <si>
-    <t>Diagramma Scuola Database</t>
-  </si>
-  <si>
-    <t>&lt;BINARY DATA&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="353">
   <si>
     <t>StudenteId</t>
   </si>
@@ -1436,10 +1414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1455,22 +1433,850 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
       </c>
       <c r="E2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="1">
+        <v>36234</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1">
+        <v>37299</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1">
+        <v>37703</v>
+      </c>
+      <c r="E5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1">
+        <v>38091</v>
+      </c>
+      <c r="E6" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
         <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="1">
+        <v>38477</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1">
+        <v>38874</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1">
+        <v>36535</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>36234</v>
+      </c>
+      <c r="E10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1">
+        <v>37092</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1">
+        <v>36104</v>
+      </c>
+      <c r="E12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="1">
+        <v>37315</v>
+      </c>
+      <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1">
+        <v>36689</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="1">
+        <v>35682</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1">
+        <v>36999</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="1">
+        <v>36524</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1">
+        <v>37482</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="1">
+        <v>36800</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="1">
+        <v>35817</v>
+      </c>
+      <c r="E21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G21" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="1">
+        <v>37016</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="1">
+        <v>36358</v>
+      </c>
+      <c r="E23" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G24" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="1">
+        <v>36588</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="1">
+        <v>35606</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="1">
+        <v>37510</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="1">
+        <v>35833</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="1">
+        <v>37214</v>
+      </c>
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="1">
+        <v>36273</v>
+      </c>
+      <c r="E30" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="1">
+        <v>36872</v>
+      </c>
+      <c r="E31" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" t="s">
+        <v>134</v>
+      </c>
+      <c r="G31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="1">
+        <v>35672</v>
+      </c>
+      <c r="E32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F32" t="s">
+        <v>135</v>
+      </c>
+      <c r="G32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="1">
+        <v>37265</v>
+      </c>
+      <c r="E33" t="s">
+        <v>99</v>
+      </c>
+      <c r="F33" t="s">
+        <v>136</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="1">
+        <v>35931</v>
+      </c>
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="1">
+        <v>37048</v>
+      </c>
+      <c r="E35" t="s">
+        <v>101</v>
+      </c>
+      <c r="F35" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" t="s">
+        <v>139</v>
+      </c>
+      <c r="G36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="1">
+        <v>36796</v>
+      </c>
+      <c r="E37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F37" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="1">
+        <v>36443</v>
+      </c>
+      <c r="E38" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -1480,869 +2286,534 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>182</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>214</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="1">
-        <v>36234</v>
-      </c>
-      <c r="E3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>215</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="1">
-        <v>37299</v>
-      </c>
-      <c r="E4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>216</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="1">
-        <v>37703</v>
-      </c>
-      <c r="E5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>217</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>188</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1">
-        <v>38091</v>
-      </c>
-      <c r="E6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>218</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1">
-        <v>38477</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>219</v>
+      </c>
+      <c r="D7">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1">
-        <v>38874</v>
-      </c>
-      <c r="E8" t="s">
-        <v>81</v>
-      </c>
-      <c r="F8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>220</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="1">
-        <v>36535</v>
-      </c>
-      <c r="E9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>221</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="1">
-        <v>36234</v>
-      </c>
-      <c r="E10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>222</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="1">
-        <v>37092</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>223</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="1">
-        <v>36104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>85</v>
-      </c>
-      <c r="F12" t="s">
-        <v>122</v>
-      </c>
-      <c r="G12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>224</v>
+      </c>
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="1">
-        <v>37315</v>
-      </c>
-      <c r="E13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" t="s">
-        <v>123</v>
-      </c>
-      <c r="G13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>225</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" t="s">
-        <v>124</v>
-      </c>
-      <c r="G14" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>226</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>197</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="1">
-        <v>36689</v>
-      </c>
-      <c r="E15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" t="s">
-        <v>125</v>
-      </c>
-      <c r="G15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>227</v>
+      </c>
+      <c r="D15">
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="1">
-        <v>35682</v>
-      </c>
-      <c r="E16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>228</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="1">
-        <v>36999</v>
-      </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>229</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="C18" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18">
+        <v>8</v>
+      </c>
+      <c r="E18">
         <v>55</v>
       </c>
-      <c r="D18" s="1">
-        <v>36524</v>
-      </c>
-      <c r="E18" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G18" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="1">
-        <v>37482</v>
-      </c>
-      <c r="E19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F19" t="s">
-        <v>129</v>
-      </c>
-      <c r="G19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>231</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>202</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="1">
-        <v>36800</v>
-      </c>
-      <c r="E20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>232</v>
+      </c>
+      <c r="D20">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="1">
-        <v>35817</v>
-      </c>
-      <c r="E21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>233</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>204</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="1">
-        <v>37016</v>
-      </c>
-      <c r="E22" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" t="s">
-        <v>132</v>
-      </c>
-      <c r="G22" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>234</v>
+      </c>
+      <c r="D22">
+        <v>8</v>
+      </c>
+      <c r="E22">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>205</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="1">
-        <v>36358</v>
-      </c>
-      <c r="E23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F23" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>235</v>
+      </c>
+      <c r="D23">
+        <v>9</v>
+      </c>
+      <c r="E23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>236</v>
+      </c>
+      <c r="D24">
+        <v>9</v>
+      </c>
+      <c r="E24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="1">
-        <v>36588</v>
-      </c>
-      <c r="E25" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" t="s">
-        <v>135</v>
-      </c>
-      <c r="G25" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>237</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" s="1">
-        <v>35606</v>
-      </c>
-      <c r="E26" t="s">
-        <v>99</v>
-      </c>
-      <c r="F26" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>238</v>
+      </c>
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="1">
-        <v>37510</v>
-      </c>
-      <c r="E27" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>239</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>210</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="1">
-        <v>35833</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
-      </c>
-      <c r="F28" t="s">
-        <v>138</v>
-      </c>
-      <c r="G28" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>240</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="C29" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
         <v>65</v>
       </c>
-      <c r="D29" s="1">
-        <v>37214</v>
-      </c>
-      <c r="E29" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" t="s">
-        <v>139</v>
-      </c>
-      <c r="G29" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>212</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="1">
-        <v>36273</v>
-      </c>
-      <c r="E30" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" t="s">
-        <v>140</v>
-      </c>
-      <c r="G30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>241</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="1">
-        <v>36872</v>
-      </c>
-      <c r="E31" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="1">
-        <v>35672</v>
-      </c>
-      <c r="E32" t="s">
-        <v>105</v>
-      </c>
-      <c r="F32" t="s">
-        <v>142</v>
-      </c>
-      <c r="G32" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="1">
-        <v>37265</v>
-      </c>
-      <c r="E33" t="s">
-        <v>106</v>
-      </c>
-      <c r="F33" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="1">
-        <v>35931</v>
-      </c>
-      <c r="E34" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" t="s">
-        <v>144</v>
-      </c>
-      <c r="G34" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="1">
-        <v>37048</v>
-      </c>
-      <c r="E35" t="s">
-        <v>108</v>
-      </c>
-      <c r="F35" t="s">
-        <v>145</v>
-      </c>
-      <c r="G35" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" t="s">
-        <v>109</v>
-      </c>
-      <c r="F36" t="s">
-        <v>146</v>
-      </c>
-      <c r="G36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="1">
-        <v>36796</v>
-      </c>
-      <c r="E37" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="1">
-        <v>36443</v>
-      </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" t="s">
-        <v>148</v>
-      </c>
-      <c r="G38" t="s">
-        <v>185</v>
+        <v>242</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2357,19 +2828,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2377,16 +2848,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>40</v>
+        <v>260</v>
+      </c>
+      <c r="D2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E2" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2394,16 +2865,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2411,16 +2882,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
+        <v>261</v>
+      </c>
+      <c r="D4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2428,16 +2899,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2445,16 +2916,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2462,16 +2933,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7">
-        <v>60</v>
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E7" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2479,16 +2950,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
-      <c r="E8">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E8" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2496,16 +2967,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>80</v>
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2513,16 +2984,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
+        <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
+        <v>262</v>
+      </c>
+      <c r="D10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2530,16 +3001,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="D11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E11" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2547,16 +3018,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>201</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12">
-        <v>65</v>
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E12" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2564,16 +3035,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-      <c r="E13">
-        <v>70</v>
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2581,16 +3052,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>75</v>
+        <v>50</v>
+      </c>
+      <c r="D14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2598,16 +3069,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15">
-        <v>8</v>
-      </c>
-      <c r="E15">
-        <v>50</v>
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E15" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2615,16 +3086,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>235</v>
-      </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="D16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2632,16 +3103,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>45</v>
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2649,16 +3120,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>237</v>
-      </c>
-      <c r="D18">
-        <v>8</v>
-      </c>
-      <c r="E18">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="D18" t="s">
+        <v>280</v>
+      </c>
+      <c r="E18" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2666,16 +3137,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>238</v>
-      </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19">
-        <v>40</v>
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2683,16 +3154,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D20">
-        <v>10</v>
-      </c>
-      <c r="E20">
-        <v>80</v>
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2700,16 +3171,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="C21" t="s">
-        <v>240</v>
-      </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
-      <c r="E21">
-        <v>50</v>
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
+        <v>283</v>
+      </c>
+      <c r="E21" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2717,16 +3188,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22">
-        <v>8</v>
-      </c>
-      <c r="E22">
-        <v>60</v>
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>284</v>
+      </c>
+      <c r="E22" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2734,16 +3205,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s">
-        <v>242</v>
-      </c>
-      <c r="D23">
-        <v>9</v>
-      </c>
-      <c r="E23">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>285</v>
+      </c>
+      <c r="E23" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2751,16 +3222,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="C24" t="s">
-        <v>243</v>
-      </c>
-      <c r="D24">
-        <v>9</v>
-      </c>
-      <c r="E24">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>286</v>
+      </c>
+      <c r="E24" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2768,16 +3239,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="C25" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25">
-        <v>8</v>
-      </c>
-      <c r="E25">
-        <v>55</v>
+        <v>38</v>
+      </c>
+      <c r="D25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E25" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2785,16 +3256,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="C26" t="s">
-        <v>245</v>
-      </c>
-      <c r="D26">
-        <v>10</v>
-      </c>
-      <c r="E26">
-        <v>75</v>
+        <v>63</v>
+      </c>
+      <c r="D26" t="s">
+        <v>288</v>
+      </c>
+      <c r="E26" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2802,16 +3273,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <v>70</v>
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>289</v>
+      </c>
+      <c r="E27" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2819,16 +3290,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
-        <v>247</v>
-      </c>
-      <c r="D28">
-        <v>10</v>
-      </c>
-      <c r="E28">
-        <v>80</v>
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2836,16 +3307,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
-      <c r="E29">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="D29" t="s">
+        <v>291</v>
+      </c>
+      <c r="E29" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2853,16 +3324,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
-      </c>
-      <c r="D30">
-        <v>5</v>
-      </c>
-      <c r="E30">
-        <v>30</v>
+        <v>48</v>
+      </c>
+      <c r="D30" t="s">
+        <v>292</v>
+      </c>
+      <c r="E30" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2870,16 +3341,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>249</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
-      </c>
-      <c r="E31">
-        <v>75</v>
+        <v>263</v>
+      </c>
+      <c r="D31" t="s">
+        <v>293</v>
+      </c>
+      <c r="E31" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -2889,534 +3360,348 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>313</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>314</v>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>315</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>316</v>
+      </c>
+      <c r="C5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" t="s">
-        <v>275</v>
-      </c>
-      <c r="E6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>317</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>318</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>277</v>
-      </c>
-      <c r="E8" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9">
         <v>15</v>
       </c>
-      <c r="C9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" t="s">
-        <v>279</v>
-      </c>
-      <c r="E10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>321</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>322</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D12" t="s">
-        <v>281</v>
-      </c>
-      <c r="E12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>323</v>
+      </c>
+      <c r="C12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>282</v>
-      </c>
-      <c r="E13" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>324</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>283</v>
-      </c>
-      <c r="E14" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>325</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>284</v>
-      </c>
-      <c r="E15" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>326</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>285</v>
-      </c>
-      <c r="E16" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>327</v>
+      </c>
+      <c r="C16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
-      </c>
-      <c r="C17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" t="s">
-        <v>286</v>
-      </c>
-      <c r="E17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>328</v>
+      </c>
+      <c r="C17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>287</v>
-      </c>
-      <c r="E18" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>329</v>
+      </c>
+      <c r="C18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>288</v>
-      </c>
-      <c r="E19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>330</v>
+      </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>289</v>
-      </c>
-      <c r="E20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>331</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
-      </c>
-      <c r="C21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" t="s">
-        <v>290</v>
-      </c>
-      <c r="E21" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>332</v>
+      </c>
+      <c r="C21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>291</v>
-      </c>
-      <c r="E22" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>333</v>
+      </c>
+      <c r="C22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>259</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" t="s">
-        <v>292</v>
-      </c>
-      <c r="E23" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>334</v>
+      </c>
+      <c r="C23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>260</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>293</v>
-      </c>
-      <c r="E24" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>335</v>
+      </c>
+      <c r="C24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" t="s">
-        <v>294</v>
-      </c>
-      <c r="E25" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>336</v>
+      </c>
+      <c r="C25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>295</v>
-      </c>
-      <c r="E26" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>337</v>
+      </c>
+      <c r="C26">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>296</v>
-      </c>
-      <c r="E27" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>338</v>
+      </c>
+      <c r="C27">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C28" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" t="s">
-        <v>297</v>
-      </c>
-      <c r="E28" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>339</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>264</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" t="s">
-        <v>298</v>
-      </c>
-      <c r="E29" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>340</v>
+      </c>
+      <c r="C29">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>265</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" t="s">
-        <v>299</v>
-      </c>
-      <c r="E30" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>341</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
-      </c>
-      <c r="C31" t="s">
-        <v>270</v>
-      </c>
-      <c r="D31" t="s">
-        <v>300</v>
-      </c>
-      <c r="E31" t="s">
-        <v>301</v>
+        <v>342</v>
+      </c>
+      <c r="C31">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -3426,348 +3711,413 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="B1" t="s">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>179</v>
+      </c>
+      <c r="D1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>320</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>321</v>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>322</v>
+      <c r="B4">
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>323</v>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>45304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>324</v>
+      <c r="B6">
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>325</v>
+      <c r="B7">
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1">
+        <v>45308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>326</v>
+      <c r="B8">
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>327</v>
+      <c r="B9">
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45310</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>328</v>
+      <c r="B10">
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>329</v>
+      <c r="B11">
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>330</v>
+      <c r="B12">
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>331</v>
+      <c r="B13">
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>332</v>
+      <c r="B14">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1">
+        <v>45315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>333</v>
+      <c r="B15">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="D15" s="1">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>334</v>
+      <c r="B16">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="D16" s="1">
+        <v>45317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>335</v>
+      <c r="B17">
+        <v>18</v>
       </c>
       <c r="C17">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1">
+        <v>45318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>336</v>
+      <c r="B18">
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1">
+        <v>45319</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>337</v>
+      <c r="B19">
+        <v>20</v>
       </c>
       <c r="C19">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1">
+        <v>45320</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>338</v>
+      <c r="B20">
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="D20" s="1">
+        <v>45321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>339</v>
+      <c r="B21">
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>340</v>
+      <c r="B22">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>23</v>
+      </c>
+      <c r="D22" s="1">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>341</v>
+      <c r="B23">
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>24</v>
+      </c>
+      <c r="D23" s="1">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>342</v>
+      <c r="B24">
+        <v>25</v>
       </c>
       <c r="C24">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="1">
+        <v>45325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>343</v>
+      <c r="B25">
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="D25" s="1">
+        <v>45326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>344</v>
+      <c r="B26">
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>345</v>
+      <c r="B27">
+        <v>28</v>
       </c>
       <c r="C27">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>28</v>
+      </c>
+      <c r="D27" s="1">
+        <v>45328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>346</v>
+      <c r="B28">
+        <v>29</v>
       </c>
       <c r="C28">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>29</v>
+      </c>
+      <c r="D28" s="1">
+        <v>45329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>347</v>
+      <c r="B29">
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>348</v>
-      </c>
-      <c r="C30">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>349</v>
-      </c>
-      <c r="C31">
-        <v>35</v>
+      <c r="D29" s="1">
+        <v>45330</v>
       </c>
     </row>
   </sheetData>
@@ -3777,24 +4127,30 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>179</v>
       </c>
       <c r="C1" t="s">
-        <v>186</v>
+        <v>310</v>
       </c>
       <c r="D1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>346</v>
+      </c>
+      <c r="E1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3805,10 +4161,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>45301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>45352</v>
+      </c>
+      <c r="E2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3819,10 +4181,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="1">
-        <v>45302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>45352</v>
+      </c>
+      <c r="E3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3833,10 +4201,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="1">
-        <v>45303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>45353</v>
+      </c>
+      <c r="E4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3847,343 +4221,453 @@
         <v>4</v>
       </c>
       <c r="D5" s="1">
-        <v>45304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>45353</v>
+      </c>
+      <c r="E5" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
-        <v>45307</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>45354</v>
+      </c>
+      <c r="E6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1">
-        <v>45308</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>45354</v>
+      </c>
+      <c r="E7" t="s">
+        <v>350</v>
+      </c>
+      <c r="F7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1">
-        <v>45309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>45357</v>
+      </c>
+      <c r="E8" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1">
-        <v>45310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>45357</v>
+      </c>
+      <c r="E9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1">
-        <v>45311</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>45358</v>
+      </c>
+      <c r="E10" t="s">
+        <v>349</v>
+      </c>
+      <c r="F10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1">
-        <v>45312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>45358</v>
+      </c>
+      <c r="E11" t="s">
+        <v>350</v>
+      </c>
+      <c r="F11" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1">
-        <v>45313</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>45359</v>
+      </c>
+      <c r="E12" t="s">
+        <v>349</v>
+      </c>
+      <c r="F12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13" s="1">
-        <v>45314</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>45359</v>
+      </c>
+      <c r="E13" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
-        <v>45315</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>45360</v>
+      </c>
+      <c r="E14" t="s">
+        <v>349</v>
+      </c>
+      <c r="F14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D15" s="1">
-        <v>45316</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>45360</v>
+      </c>
+      <c r="E15" t="s">
+        <v>350</v>
+      </c>
+      <c r="F15" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1">
-        <v>45317</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+        <v>45361</v>
+      </c>
+      <c r="E16" t="s">
+        <v>349</v>
+      </c>
+      <c r="F16" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1">
-        <v>45318</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>45361</v>
+      </c>
+      <c r="E17" t="s">
+        <v>350</v>
+      </c>
+      <c r="F17" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D18" s="1">
-        <v>45319</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
+        <v>45362</v>
+      </c>
+      <c r="E18" t="s">
+        <v>349</v>
+      </c>
+      <c r="F18" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D19" s="1">
-        <v>45320</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>45362</v>
+      </c>
+      <c r="E19" t="s">
+        <v>350</v>
+      </c>
+      <c r="F19" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D20" s="1">
-        <v>45321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>45363</v>
+      </c>
+      <c r="E20" t="s">
+        <v>349</v>
+      </c>
+      <c r="F20" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D21" s="1">
-        <v>45322</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>45363</v>
+      </c>
+      <c r="E21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1">
-        <v>45323</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
+        <v>45364</v>
+      </c>
+      <c r="E22" t="s">
+        <v>349</v>
+      </c>
+      <c r="F22" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1">
-        <v>45324</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>45364</v>
+      </c>
+      <c r="E23" t="s">
+        <v>350</v>
+      </c>
+      <c r="F23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1">
-        <v>45325</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>45365</v>
+      </c>
+      <c r="E24" t="s">
+        <v>349</v>
+      </c>
+      <c r="F24" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1">
-        <v>45326</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>45365</v>
+      </c>
+      <c r="E25" t="s">
+        <v>350</v>
+      </c>
+      <c r="F25" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D26" s="1">
-        <v>45327</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>45366</v>
+      </c>
+      <c r="E26" t="s">
+        <v>349</v>
+      </c>
+      <c r="F26" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1">
-        <v>45328</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>29</v>
-      </c>
-      <c r="C28">
-        <v>29</v>
-      </c>
-      <c r="D28" s="1">
-        <v>45329</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>30</v>
-      </c>
-      <c r="C29">
-        <v>30</v>
-      </c>
-      <c r="D29" s="1">
-        <v>45330</v>
+        <v>45366</v>
+      </c>
+      <c r="E27" t="s">
+        <v>350</v>
+      </c>
+      <c r="F27" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -4193,568 +4677,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1">
-        <v>45352</v>
-      </c>
-      <c r="E2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>45352</v>
-      </c>
-      <c r="E3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F3" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1">
-        <v>45353</v>
-      </c>
-      <c r="E4" t="s">
-        <v>356</v>
-      </c>
-      <c r="F4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1">
-        <v>45353</v>
-      </c>
-      <c r="E5" t="s">
-        <v>357</v>
-      </c>
-      <c r="F5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1">
-        <v>45354</v>
-      </c>
-      <c r="E6" t="s">
-        <v>356</v>
-      </c>
-      <c r="F6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1">
-        <v>45354</v>
-      </c>
-      <c r="E7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1">
-        <v>45357</v>
-      </c>
-      <c r="E8" t="s">
-        <v>356</v>
-      </c>
-      <c r="F8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1">
-        <v>45357</v>
-      </c>
-      <c r="E9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F9" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>13</v>
-      </c>
-      <c r="C10">
-        <v>13</v>
-      </c>
-      <c r="D10" s="1">
-        <v>45358</v>
-      </c>
-      <c r="E10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F10" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>14</v>
-      </c>
-      <c r="C11">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1">
-        <v>45358</v>
-      </c>
-      <c r="E11" t="s">
-        <v>357</v>
-      </c>
-      <c r="F11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>15</v>
-      </c>
-      <c r="D12" s="1">
-        <v>45359</v>
-      </c>
-      <c r="E12" t="s">
-        <v>356</v>
-      </c>
-      <c r="F12" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>16</v>
-      </c>
-      <c r="C13">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1">
-        <v>45359</v>
-      </c>
-      <c r="E13" t="s">
-        <v>357</v>
-      </c>
-      <c r="F13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>17</v>
-      </c>
-      <c r="C14">
-        <v>17</v>
-      </c>
-      <c r="D14" s="1">
-        <v>45360</v>
-      </c>
-      <c r="E14" t="s">
-        <v>356</v>
-      </c>
-      <c r="F14" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>18</v>
-      </c>
-      <c r="C15">
-        <v>18</v>
-      </c>
-      <c r="D15" s="1">
-        <v>45360</v>
-      </c>
-      <c r="E15" t="s">
-        <v>357</v>
-      </c>
-      <c r="F15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>19</v>
-      </c>
-      <c r="C16">
-        <v>19</v>
-      </c>
-      <c r="D16" s="1">
-        <v>45361</v>
-      </c>
-      <c r="E16" t="s">
-        <v>356</v>
-      </c>
-      <c r="F16" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>20</v>
-      </c>
-      <c r="C17">
-        <v>20</v>
-      </c>
-      <c r="D17" s="1">
-        <v>45361</v>
-      </c>
-      <c r="E17" t="s">
-        <v>357</v>
-      </c>
-      <c r="F17" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>21</v>
-      </c>
-      <c r="C18">
-        <v>21</v>
-      </c>
-      <c r="D18" s="1">
-        <v>45362</v>
-      </c>
-      <c r="E18" t="s">
-        <v>356</v>
-      </c>
-      <c r="F18" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>22</v>
-      </c>
-      <c r="C19">
-        <v>22</v>
-      </c>
-      <c r="D19" s="1">
-        <v>45362</v>
-      </c>
-      <c r="E19" t="s">
-        <v>357</v>
-      </c>
-      <c r="F19" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>23</v>
-      </c>
-      <c r="C20">
-        <v>23</v>
-      </c>
-      <c r="D20" s="1">
-        <v>45363</v>
-      </c>
-      <c r="E20" t="s">
-        <v>356</v>
-      </c>
-      <c r="F20" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>24</v>
-      </c>
-      <c r="C21">
-        <v>24</v>
-      </c>
-      <c r="D21" s="1">
-        <v>45363</v>
-      </c>
-      <c r="E21" t="s">
-        <v>357</v>
-      </c>
-      <c r="F21" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>25</v>
-      </c>
-      <c r="C22">
-        <v>25</v>
-      </c>
-      <c r="D22" s="1">
-        <v>45364</v>
-      </c>
-      <c r="E22" t="s">
-        <v>356</v>
-      </c>
-      <c r="F22" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>26</v>
-      </c>
-      <c r="C23">
-        <v>26</v>
-      </c>
-      <c r="D23" s="1">
-        <v>45364</v>
-      </c>
-      <c r="E23" t="s">
-        <v>357</v>
-      </c>
-      <c r="F23" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>27</v>
-      </c>
-      <c r="C24">
-        <v>27</v>
-      </c>
-      <c r="D24" s="1">
-        <v>45365</v>
-      </c>
-      <c r="E24" t="s">
-        <v>356</v>
-      </c>
-      <c r="F24" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>28</v>
-      </c>
-      <c r="C25">
-        <v>28</v>
-      </c>
-      <c r="D25" s="1">
-        <v>45365</v>
-      </c>
-      <c r="E25" t="s">
-        <v>357</v>
-      </c>
-      <c r="F25" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>29</v>
-      </c>
-      <c r="C26">
-        <v>29</v>
-      </c>
-      <c r="D26" s="1">
-        <v>45366</v>
-      </c>
-      <c r="E26" t="s">
-        <v>356</v>
-      </c>
-      <c r="F26" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>30</v>
-      </c>
-      <c r="C27">
-        <v>30</v>
-      </c>
-      <c r="D27" s="1">
-        <v>45366</v>
-      </c>
-      <c r="E27" t="s">
-        <v>357</v>
-      </c>
-      <c r="F27" t="s">
-        <v>358</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:3">

--- a/Report_ScuolaDb.xlsx
+++ b/Report_ScuolaDb.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="358">
   <si>
     <t>StudenteId</t>
   </si>
@@ -133,6 +133,9 @@
     <t>Emanuele</t>
   </si>
   <si>
+    <t>Sandra</t>
+  </si>
+  <si>
     <t>Rossi</t>
   </si>
   <si>
@@ -226,6 +229,9 @@
     <t>Villa</t>
   </si>
   <si>
+    <t>Miranda</t>
+  </si>
+  <si>
     <t>mario2.rossi@libero.it</t>
   </si>
   <si>
@@ -337,6 +343,9 @@
     <t>emanuele.villa@email.com</t>
   </si>
   <si>
+    <t>sandra.miranda@gmail.com</t>
+  </si>
+  <si>
     <t>+393874665</t>
   </si>
   <si>
@@ -448,6 +457,9 @@
     <t>300000030</t>
   </si>
   <si>
+    <t>3935426213</t>
+  </si>
+  <si>
     <t xml:space="preserve">HFJFNVJIEIWJSFB </t>
   </si>
   <si>
@@ -557,6 +569,9 @@
   </si>
   <si>
     <t>VLLMNL99R10H501D</t>
+  </si>
+  <si>
+    <t>MRDSMR88189PY000</t>
   </si>
   <si>
     <t>CorsoId</t>
@@ -1414,7 +1429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1448,16 +1463,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1468,19 +1483,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1">
         <v>36234</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1491,19 +1506,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1">
         <v>37299</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1514,19 +1529,19 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
         <v>37703</v>
       </c>
       <c r="E5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1537,19 +1552,19 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1">
         <v>38091</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1560,19 +1575,19 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1">
         <v>38477</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1583,19 +1598,19 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1">
         <v>38874</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G8" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1606,19 +1621,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1">
         <v>36535</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1629,19 +1644,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>36234</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1652,19 +1667,19 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1">
         <v>37092</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1675,19 +1690,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="1">
         <v>36104</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1698,19 +1713,19 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1">
         <v>37315</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1721,16 +1736,16 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1741,19 +1756,19 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="1">
         <v>36689</v>
       </c>
       <c r="E15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1764,19 +1779,19 @@
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="1">
         <v>35682</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1787,19 +1802,19 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="1">
         <v>36999</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1810,19 +1825,19 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18" s="1">
         <v>36524</v>
       </c>
       <c r="E18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1833,19 +1848,19 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1">
         <v>37482</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1856,19 +1871,19 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1">
         <v>36800</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1879,19 +1894,19 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1">
         <v>35817</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1902,19 +1917,19 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1">
         <v>37016</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G22" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1925,19 +1940,19 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1">
         <v>36358</v>
       </c>
       <c r="E23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G23" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1948,16 +1963,16 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1968,19 +1983,19 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1">
         <v>36588</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1991,19 +2006,19 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="1">
         <v>35606</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F26" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2014,19 +2029,19 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1">
         <v>37510</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2037,19 +2052,19 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1">
         <v>35833</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2060,19 +2075,19 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="1">
         <v>37214</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2083,19 +2098,19 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1">
         <v>36273</v>
       </c>
       <c r="E30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2106,19 +2121,19 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" s="1">
         <v>36872</v>
       </c>
       <c r="E31" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2129,19 +2144,19 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D32" s="1">
         <v>35672</v>
       </c>
       <c r="E32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G32" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2152,19 +2167,19 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1">
         <v>37265</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2175,19 +2190,19 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D34" s="1">
         <v>35931</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2198,19 +2213,19 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D35" s="1">
         <v>37048</v>
       </c>
       <c r="E35" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F35" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2221,16 +2236,16 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F36" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G36" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2241,19 +2256,19 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" s="1">
         <v>36796</v>
       </c>
       <c r="E37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F37" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2264,19 +2279,42 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D38" s="1">
         <v>36443</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F38" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G38" t="s">
-        <v>178</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="1">
+        <v>32183</v>
+      </c>
+      <c r="E39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F39" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -2291,19 +2329,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2311,10 +2349,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D2">
         <v>6</v>
@@ -2328,10 +2366,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D3">
         <v>8</v>
@@ -2345,10 +2383,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -2362,10 +2400,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -2379,10 +2417,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -2396,10 +2434,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -2413,10 +2451,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -2430,10 +2468,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D9">
         <v>10</v>
@@ -2447,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -2464,10 +2502,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -2481,10 +2519,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -2498,10 +2536,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -2515,10 +2553,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -2532,10 +2570,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C15" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -2549,10 +2587,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C16" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -2566,10 +2604,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D17">
         <v>7</v>
@@ -2583,10 +2621,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D18">
         <v>8</v>
@@ -2600,10 +2638,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D19">
         <v>6</v>
@@ -2617,10 +2655,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -2634,10 +2672,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2651,10 +2689,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C22" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2668,10 +2706,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D23">
         <v>9</v>
@@ -2685,10 +2723,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C24" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D24">
         <v>9</v>
@@ -2702,10 +2740,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -2719,10 +2757,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C26" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -2736,10 +2774,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D27">
         <v>10</v>
@@ -2753,10 +2791,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C28" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D28">
         <v>10</v>
@@ -2770,10 +2808,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2787,10 +2825,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -2804,10 +2842,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C31" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D31">
         <v>10</v>
@@ -2828,7 +2866,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2840,7 +2878,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2848,16 +2886,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2865,16 +2903,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2885,13 +2923,13 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2902,13 +2940,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -2919,13 +2957,13 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2936,13 +2974,13 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2953,13 +2991,13 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E8" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2970,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E9" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2984,16 +3022,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E10" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3004,13 +3042,13 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E11" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3021,13 +3059,13 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3038,13 +3076,13 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3055,13 +3093,13 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3072,13 +3110,13 @@
         <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3089,13 +3127,13 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E16" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3103,16 +3141,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E17" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3123,13 +3161,13 @@
         <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E18" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3137,16 +3175,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E19" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3157,13 +3195,13 @@
         <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3171,16 +3209,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E21" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3188,16 +3226,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E22" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3205,16 +3243,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E23" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3222,16 +3260,16 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E24" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3239,16 +3277,16 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3256,16 +3294,16 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3276,13 +3314,13 @@
         <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3290,16 +3328,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E28" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3307,16 +3345,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3324,16 +3362,16 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E30" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3341,16 +3379,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E31" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -3365,13 +3403,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3379,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -3390,7 +3428,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -3401,7 +3439,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C4">
         <v>20</v>
@@ -3412,7 +3450,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C5">
         <v>35</v>
@@ -3423,7 +3461,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -3434,7 +3472,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -3445,7 +3483,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -3456,7 +3494,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -3467,7 +3505,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -3478,7 +3516,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -3489,7 +3527,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3500,7 +3538,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -3511,7 +3549,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C14">
         <v>25</v>
@@ -3522,7 +3560,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -3533,7 +3571,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C16">
         <v>35</v>
@@ -3544,7 +3582,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C17">
         <v>40</v>
@@ -3555,7 +3593,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="C18">
         <v>20</v>
@@ -3566,7 +3604,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C19">
         <v>20</v>
@@ -3577,7 +3615,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C20">
         <v>15</v>
@@ -3588,7 +3626,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C21">
         <v>25</v>
@@ -3599,7 +3637,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -3610,7 +3648,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -3621,7 +3659,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C24">
         <v>25</v>
@@ -3632,7 +3670,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C25">
         <v>20</v>
@@ -3643,7 +3681,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C26">
         <v>35</v>
@@ -3654,7 +3692,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C27">
         <v>40</v>
@@ -3665,7 +3703,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -3676,7 +3714,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C29">
         <v>25</v>
@@ -3687,7 +3725,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C30">
         <v>20</v>
@@ -3698,7 +3736,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C31">
         <v>35</v>
@@ -3716,16 +3754,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4132,22 +4170,22 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E1" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="F1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4164,10 +4202,10 @@
         <v>45352</v>
       </c>
       <c r="E2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4184,10 +4222,10 @@
         <v>45352</v>
       </c>
       <c r="E3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4204,10 +4242,10 @@
         <v>45353</v>
       </c>
       <c r="E4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F4" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4224,10 +4262,10 @@
         <v>45353</v>
       </c>
       <c r="E5" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F5" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4244,10 +4282,10 @@
         <v>45354</v>
       </c>
       <c r="E6" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4264,10 +4302,10 @@
         <v>45354</v>
       </c>
       <c r="E7" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F7" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4284,10 +4322,10 @@
         <v>45357</v>
       </c>
       <c r="E8" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F8" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4304,10 +4342,10 @@
         <v>45357</v>
       </c>
       <c r="E9" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4324,10 +4362,10 @@
         <v>45358</v>
       </c>
       <c r="E10" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F10" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4344,10 +4382,10 @@
         <v>45358</v>
       </c>
       <c r="E11" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F11" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4364,10 +4402,10 @@
         <v>45359</v>
       </c>
       <c r="E12" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F12" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4384,10 +4422,10 @@
         <v>45359</v>
       </c>
       <c r="E13" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F13" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4404,10 +4442,10 @@
         <v>45360</v>
       </c>
       <c r="E14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F14" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4424,10 +4462,10 @@
         <v>45360</v>
       </c>
       <c r="E15" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F15" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4444,10 +4482,10 @@
         <v>45361</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F16" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4464,10 +4502,10 @@
         <v>45361</v>
       </c>
       <c r="E17" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F17" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4484,10 +4522,10 @@
         <v>45362</v>
       </c>
       <c r="E18" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F18" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4504,10 +4542,10 @@
         <v>45362</v>
       </c>
       <c r="E19" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F19" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4524,10 +4562,10 @@
         <v>45363</v>
       </c>
       <c r="E20" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F20" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4544,10 +4582,10 @@
         <v>45363</v>
       </c>
       <c r="E21" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F21" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4564,10 +4602,10 @@
         <v>45364</v>
       </c>
       <c r="E22" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F22" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4584,10 +4622,10 @@
         <v>45364</v>
       </c>
       <c r="E23" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F23" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4604,10 +4642,10 @@
         <v>45365</v>
       </c>
       <c r="E24" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F24" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4624,10 +4662,10 @@
         <v>45365</v>
       </c>
       <c r="E25" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F25" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4644,10 +4682,10 @@
         <v>45366</v>
       </c>
       <c r="E26" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F26" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4664,10 +4702,10 @@
         <v>45366</v>
       </c>
       <c r="E27" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F27" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4682,13 +4720,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:3">
